--- a/backend/data/uploads/MES/2026-07-13_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-13_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{31A956C3-1238-4FC9-BA8B-D157E82EA60C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2011BAA1-0E9C-453C-A0D8-A488194AEEEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{EDAC7FED-B24E-4EC7-AD68-93D986C032D4}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{EEBB5540-5C3D-4E83-81C2-C28C373AF404}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5A11AF6-20D8-4913-8E5E-9DFB9341E100}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CC407FB-6C79-45B3-BEEF-F3655BA93862}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-13_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-13_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2011BAA1-0E9C-453C-A0D8-A488194AEEEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A434B4B6-2D4C-4180-8A1D-C1DEDD906700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{EEBB5540-5C3D-4E83-81C2-C28C373AF404}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{BC02EAB3-7C14-411D-969D-5A8240EFDD69}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CC407FB-6C79-45B3-BEEF-F3655BA93862}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3E8D8D6-AF99-4729-850A-6EB57A92E8B1}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-13_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-13_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A434B4B6-2D4C-4180-8A1D-C1DEDD906700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9257D591-C2AF-430D-ADD4-D7099F7BC7D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{BC02EAB3-7C14-411D-969D-5A8240EFDD69}"/>
+    <workbookView xWindow="-30240" yWindow="8376" windowWidth="23040" windowHeight="12012" xr2:uid="{FAE29C67-6077-429E-879D-A0AD5FF65552}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3E8D8D6-AF99-4729-850A-6EB57A92E8B1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23277095-F2FE-403C-A7CD-F801B49130AA}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
